--- a/SuppXLS/Scen_advanced_features.xlsx
+++ b/SuppXLS/Scen_advanced_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VerveStacks\Assumptions\VerveStacks_ISO_template\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B6907D-6C39-452D-B64B-38F32025EB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920EC741-2359-4037-B5DD-4DA8F28C0E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17596" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="281">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2786,9 +2786,6 @@
     <t>*stg8hb*</t>
   </si>
   <si>
-    <t>ELC4H,ELC8H,ELC</t>
-  </si>
-  <si>
     <t>IN</t>
   </si>
   <si>
@@ -2801,9 +2798,6 @@
     <t>distr*</t>
   </si>
   <si>
-    <t>ELC4H,ELC8H</t>
-  </si>
-  <si>
     <t>OUT</t>
   </si>
   <si>
@@ -2865,6 +2859,15 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H,ELCnH</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>STG</t>
   </si>
 </sst>
 </file>
@@ -2944,7 +2947,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2954,12 +2957,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2996,7 +2993,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
@@ -3036,10 +3033,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
@@ -3143,9 +3136,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3183,7 +3176,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3289,7 +3282,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3431,7 +3424,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4306,49 +4299,49 @@
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.45">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="15">
         <v>0</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="15">
         <v>0.5</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="15">
         <v>1.2</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="15">
         <v>0.01</v>
       </c>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="L18" s="23">
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="L18" s="19">
         <v>30</v>
       </c>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22">
+      <c r="M18" s="15"/>
+      <c r="N18" s="15">
         <v>0.5</v>
       </c>
-      <c r="O18" s="22">
+      <c r="O18" s="15">
         <v>1.2</v>
       </c>
-      <c r="P18" s="22"/>
-      <c r="Q18" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="R18" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="S18" s="22" t="s">
-        <v>278</v>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="R18" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="S18" s="15" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4385,7 +4378,7 @@
     <col min="24" max="24" width="5" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="6" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="34" width="4" style="20" customWidth="1"/>
+    <col min="29" max="34" width="4" customWidth="1"/>
     <col min="36" max="36" width="14.53125" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="1.73046875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="4.73046875" bestFit="1" customWidth="1"/>
@@ -4472,71 +4465,71 @@
         <f>P3+1</f>
         <v>61</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3">
         <f>Q3+18</f>
         <v>79</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3">
         <f>R3+1</f>
         <v>80</v>
       </c>
-      <c r="T3" s="20">
+      <c r="T3">
         <f>S3+1</f>
         <v>81</v>
       </c>
-      <c r="U3" s="20">
+      <c r="U3">
         <f>T3+18</f>
         <v>99</v>
       </c>
-      <c r="V3" s="20">
+      <c r="V3">
         <f>U3+1</f>
         <v>100</v>
       </c>
-      <c r="W3" s="20">
+      <c r="W3">
         <f>V3+1</f>
         <v>101</v>
       </c>
-      <c r="X3" s="20">
+      <c r="X3">
         <f>W3+18</f>
         <v>119</v>
       </c>
-      <c r="Y3" s="20">
+      <c r="Y3">
         <f>X3+1</f>
         <v>120</v>
       </c>
-      <c r="Z3" s="20">
+      <c r="Z3">
         <f>Y3+1</f>
         <v>121</v>
       </c>
-      <c r="AA3" s="20">
+      <c r="AA3">
         <f>Z3+18</f>
         <v>139</v>
       </c>
-      <c r="AB3" s="20">
+      <c r="AB3">
         <f>AA3+1</f>
         <v>140</v>
       </c>
-      <c r="AC3" s="20">
+      <c r="AC3">
         <f>AB3+1</f>
         <v>141</v>
       </c>
-      <c r="AD3" s="20">
+      <c r="AD3">
         <f>AC3+18</f>
         <v>159</v>
       </c>
-      <c r="AE3" s="20">
+      <c r="AE3">
         <f>AD3+1</f>
         <v>160</v>
       </c>
-      <c r="AF3" s="20">
+      <c r="AF3">
         <f>AE3+1</f>
         <v>161</v>
       </c>
-      <c r="AG3" s="20">
+      <c r="AG3">
         <f>AF3+18</f>
         <v>179</v>
       </c>
-      <c r="AH3" s="20">
+      <c r="AH3">
         <f>AG3+1</f>
         <v>180</v>
       </c>
@@ -4603,39 +4596,39 @@
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="AZ3" s="21">
+      <c r="AZ3" s="3">
         <f t="shared" ref="AZ3:AZ5" si="1">Z3</f>
         <v>121</v>
       </c>
-      <c r="BA3" s="21">
+      <c r="BA3" s="3">
         <f t="shared" ref="BA3:BA5" si="2">AA3</f>
         <v>139</v>
       </c>
-      <c r="BB3" s="21">
+      <c r="BB3" s="3">
         <f t="shared" ref="BB3:BB5" si="3">AB3</f>
         <v>140</v>
       </c>
-      <c r="BC3" s="21">
+      <c r="BC3" s="3">
         <f t="shared" ref="BC3:BC5" si="4">AC3</f>
         <v>141</v>
       </c>
-      <c r="BD3" s="21">
+      <c r="BD3" s="3">
         <f t="shared" ref="BD3:BE5" si="5">AD3</f>
         <v>159</v>
       </c>
-      <c r="BE3" s="21">
+      <c r="BE3" s="3">
         <f t="shared" si="5"/>
         <v>160</v>
       </c>
-      <c r="BF3" s="21">
+      <c r="BF3" s="3">
         <f t="shared" ref="BF3:BF5" si="6">AF3</f>
         <v>161</v>
       </c>
-      <c r="BG3" s="21">
+      <c r="BG3" s="3">
         <f t="shared" ref="BG3:BG5" si="7">AG3</f>
         <v>179</v>
       </c>
-      <c r="BH3" s="21">
+      <c r="BH3" s="3">
         <f t="shared" ref="BH3:BH5" si="8">AH3</f>
         <v>180</v>
       </c>
@@ -4717,35 +4710,35 @@
         <f>W4</f>
         <v>1</v>
       </c>
-      <c r="AA4" s="20">
+      <c r="AA4">
         <f t="shared" ref="AA4:AE5" si="9">X4</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AB4" s="20">
+      <c r="AB4">
         <f t="shared" si="9"/>
         <v>6.18</v>
       </c>
-      <c r="AC4" s="20">
+      <c r="AC4">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AD4" s="20">
+      <c r="AD4">
         <f t="shared" si="9"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AE4" s="20">
+      <c r="AE4">
         <f t="shared" si="9"/>
         <v>6.18</v>
       </c>
-      <c r="AF4" s="20">
+      <c r="AF4">
         <f t="shared" ref="AF4:AF5" si="10">AC4</f>
         <v>1</v>
       </c>
-      <c r="AG4" s="20">
+      <c r="AG4">
         <f t="shared" ref="AG4:AG5" si="11">AD4</f>
         <v>1.1100000000000001</v>
       </c>
-      <c r="AH4" s="20">
+      <c r="AH4">
         <f t="shared" ref="AH4:AH5" si="12">AE4</f>
         <v>6.18</v>
       </c>
@@ -4813,39 +4806,39 @@
         <f t="shared" si="0"/>
         <v>6.18</v>
       </c>
-      <c r="AZ4" s="20">
+      <c r="AZ4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BA4" s="20">
+      <c r="BA4">
         <f t="shared" si="2"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BB4" s="20">
+      <c r="BB4">
         <f t="shared" si="3"/>
         <v>6.18</v>
       </c>
-      <c r="BC4" s="20">
+      <c r="BC4">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BD4" s="20">
+      <c r="BD4">
         <f t="shared" si="5"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BE4" s="20">
+      <c r="BE4">
         <f t="shared" si="5"/>
         <v>6.18</v>
       </c>
-      <c r="BF4" s="20">
+      <c r="BF4">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="BG4" s="20">
+      <c r="BG4">
         <f t="shared" si="7"/>
         <v>1.1100000000000001</v>
       </c>
-      <c r="BH4" s="20">
+      <c r="BH4">
         <f t="shared" si="8"/>
         <v>6.18</v>
       </c>
@@ -4923,39 +4916,39 @@
       <c r="Y5">
         <v>10</v>
       </c>
-      <c r="Z5" s="20">
+      <c r="Z5">
         <f>W5</f>
         <v>1</v>
       </c>
-      <c r="AA5" s="20">
+      <c r="AA5">
         <f t="shared" si="9"/>
         <v>1.48</v>
       </c>
-      <c r="AB5" s="20">
+      <c r="AB5">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AC5" s="20">
+      <c r="AC5">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AD5" s="20">
+      <c r="AD5">
         <f t="shared" si="9"/>
         <v>1.48</v>
       </c>
-      <c r="AE5" s="20">
+      <c r="AE5">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="AF5" s="20">
+      <c r="AF5">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="AG5" s="20">
+      <c r="AG5">
         <f t="shared" si="11"/>
         <v>1.48</v>
       </c>
-      <c r="AH5" s="20">
+      <c r="AH5">
         <f t="shared" si="12"/>
         <v>10</v>
       </c>
@@ -5023,39 +5016,39 @@
         <f t="shared" si="13"/>
         <v>10</v>
       </c>
-      <c r="AZ5" s="20">
+      <c r="AZ5">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BA5" s="20">
+      <c r="BA5">
         <f t="shared" si="2"/>
         <v>1.48</v>
       </c>
-      <c r="BB5" s="20">
+      <c r="BB5">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="BC5" s="20">
+      <c r="BC5">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="BD5" s="20">
+      <c r="BD5">
         <f t="shared" si="5"/>
         <v>1.48</v>
       </c>
-      <c r="BE5" s="20">
+      <c r="BE5">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="BF5" s="20">
+      <c r="BF5">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="BG5" s="20">
+      <c r="BG5">
         <f t="shared" si="7"/>
         <v>1.48</v>
       </c>
-      <c r="BH5" s="20">
+      <c r="BH5">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -7067,27 +7060,35 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7792CB6B-18A0-47FE-98AC-84F99BF1E696}">
-  <dimension ref="B3:M23"/>
+  <dimension ref="B3:M24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1328125" customWidth="1"/>
+    <col min="3" max="3" width="16.53125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B4" t="s">
+    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B4" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7096,91 +7097,92 @@
         <v>252</v>
       </c>
       <c r="C5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" t="s">
         <v>253</v>
-      </c>
-      <c r="D5" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" t="s">
         <v>255</v>
       </c>
-      <c r="C6" t="s">
-        <v>256</v>
-      </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" t="s">
         <v>257</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="17" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D7" t="s">
+    </row>
+    <row r="18" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
+    <row r="20" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="H20" s="2" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+    <row r="21" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B21" s="3" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="H20" s="19" t="s">
+      <c r="C21" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
+      <c r="E21" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C21" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="F21" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E21" t="s">
+      <c r="G21" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F21" t="s">
+      <c r="H21" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G21" t="s">
+      <c r="I21" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J21" t="s">
+      <c r="L21" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="K21" t="s">
+      <c r="M21" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="L21" t="s">
-        <v>271</v>
-      </c>
-      <c r="M21" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
+        <v>271</v>
+      </c>
+      <c r="C22" t="s">
+        <v>272</v>
+      </c>
+      <c r="E22" t="s">
         <v>273</v>
-      </c>
-      <c r="C22" t="s">
-        <v>274</v>
-      </c>
-      <c r="E22" t="s">
-        <v>275</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -7192,15 +7194,26 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J23">
         <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="C24" t="s">
+        <v>280</v>
+      </c>
+      <c r="F24" t="s">
+        <v>279</v>
+      </c>
+      <c r="I24">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/SuppXLS/Scen_advanced_features.xlsx
+++ b/SuppXLS/Scen_advanced_features.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VerveStacks\Assumptions\VerveStacks_ISO_template\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NewVEDA\Veda_models\VS_CEA_8C\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920EC741-2359-4037-B5DD-4DA8F28C0E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE04CE60-3CD8-46ED-9C88-18A418A40A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17596" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="6" xr2:uid="{22AE2797-EE70-457C-AC96-4BB7B6BD4E04}"/>
   </bookViews>
   <sheets>
     <sheet name="veda input" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="282">
   <si>
     <t>ACT_MINLD</t>
   </si>
@@ -2783,15 +2783,9 @@
     <t>io</t>
   </si>
   <si>
-    <t>*stg8hb*</t>
-  </si>
-  <si>
     <t>IN</t>
   </si>
   <si>
-    <t>*stg4hb*</t>
-  </si>
-  <si>
     <t>ELC4H,ELC</t>
   </si>
   <si>
@@ -2868,6 +2862,15 @@
   </si>
   <si>
     <t>STG</t>
+  </si>
+  <si>
+    <t>pset_Set</t>
+  </si>
+  <si>
+    <t>*8h*</t>
+  </si>
+  <si>
+    <t>*4h*</t>
   </si>
 </sst>
 </file>
@@ -4321,7 +4324,7 @@
       <c r="I18" s="15"/>
       <c r="J18" s="15"/>
       <c r="K18" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L18" s="19">
         <v>30</v>
@@ -4335,13 +4338,13 @@
       </c>
       <c r="P18" s="15"/>
       <c r="Q18" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="S18" s="15" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -7076,12 +7079,12 @@
     <col min="13" max="13" width="35.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B4" s="3" t="s">
         <v>249</v>
       </c>
@@ -7091,98 +7094,107 @@
       <c r="D4" s="3" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="E4" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" t="s">
+        <v>276</v>
+      </c>
+      <c r="D5" t="s">
         <v>252</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>278</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
         <v>254</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" t="s">
         <v>255</v>
-      </c>
-      <c r="D6" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B7" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="2:13" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="H20" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="2:13" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B21" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" t="s">
+        <v>270</v>
+      </c>
+      <c r="E22" t="s">
         <v>271</v>
-      </c>
-      <c r="C22" t="s">
-        <v>272</v>
-      </c>
-      <c r="E22" t="s">
-        <v>273</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -7194,12 +7206,12 @@
         <v>5</v>
       </c>
       <c r="M22" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.45">
       <c r="G23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -7207,10 +7219,10 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.45">
       <c r="C24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I24">
         <v>0.5</v>
